--- a/main/StructureDefinition-ConsentDomain.xlsx
+++ b/main/StructureDefinition-ConsentDomain.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4484" uniqueCount="634">
   <si>
     <t>Property</t>
   </si>
@@ -574,7 +574,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -667,6 +667,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>ResearchStudy.extension:versionFormat.id</t>
   </si>
   <si>
@@ -1281,7 +1285,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1366,7 +1370,7 @@
     <t>ResearchStudy.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1409,7 +1413,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
+    <t xml:space="preserve">Reference(PlanDefinition)
 </t>
   </si>
   <si>
@@ -1435,7 +1439,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
+    <t xml:space="preserve">Reference(ResearchStudy)
 </t>
   </si>
   <si>
@@ -1493,7 +1497,7 @@
     <t>Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -1511,7 +1515,7 @@
     <t>Codes for the stage in the progression of a therapy from initial experimental use in humans in clinical trials to post-market evaluation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-phase|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-phase</t>
   </si>
   <si>
     <t>StudyProtocolVersion.phaseCode</t>
@@ -1571,7 +1575,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
   </si>
   <si>
     <t>StudyCondition.code</t>
@@ -1648,7 +1652,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -1683,7 +1687,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Group|4.0.1)
+    <t xml:space="preserve">Reference(Group)
 </t>
   </si>
   <si>
@@ -1757,7 +1761,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1776,7 +1780,7 @@
     <t>ResearchStudy.site</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1807,7 +1811,7 @@
     <t>Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -1970,7 +1974,7 @@
     <t>Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -4548,7 +4552,7 @@
         <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
@@ -4568,10 +4572,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4683,10 +4687,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4798,13 +4802,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="C22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
@@ -4829,7 +4833,7 @@
         <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>199</v>
@@ -4915,10 +4919,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5030,10 +5034,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5147,10 +5151,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5176,13 +5180,13 @@
         <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5190,7 +5194,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>21</v>
@@ -5232,7 +5236,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>92</v>
@@ -5264,10 +5268,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5293,10 +5297,10 @@
         <v>106</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5347,7 +5351,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5379,13 +5383,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>21</v>
@@ -5410,7 +5414,7 @@
         <v>113</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M27" t="s" s="2">
         <v>199</v>
@@ -5496,10 +5500,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5611,10 +5615,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5728,10 +5732,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5757,13 +5761,13 @@
         <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5771,7 +5775,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>21</v>
@@ -5813,7 +5817,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>92</v>
@@ -5845,10 +5849,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5874,10 +5878,10 @@
         <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5928,7 +5932,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5960,10 +5964,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5989,13 +5993,13 @@
         <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6003,7 +6007,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>21</v>
@@ -6045,7 +6049,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>92</v>
@@ -6077,10 +6081,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6103,13 +6107,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6160,7 +6164,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6192,19 +6196,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>81</v>
@@ -6222,13 +6226,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6291,7 +6295,7 @@
         <v>207</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>21</v>
@@ -6311,10 +6315,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6426,10 +6430,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6543,10 +6547,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6572,13 +6576,13 @@
         <v>139</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6586,7 +6590,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>21</v>
@@ -6628,7 +6632,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>92</v>
@@ -6660,10 +6664,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6686,13 +6690,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6743,7 +6747,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6775,19 +6779,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>92</v>
@@ -6805,13 +6809,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6874,7 +6878,7 @@
         <v>207</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>21</v>
@@ -6894,10 +6898,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7009,10 +7013,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7124,13 +7128,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>21</v>
@@ -7241,10 +7245,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7356,10 +7360,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7473,10 +7477,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7502,13 +7506,13 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7516,7 +7520,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>21</v>
@@ -7558,7 +7562,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>92</v>
@@ -7590,10 +7594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7619,10 +7623,10 @@
         <v>151</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7649,11 +7653,11 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7671,7 +7675,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7703,13 +7707,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>21</v>
@@ -7820,10 +7824,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7935,10 +7939,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8052,10 +8056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8081,13 +8085,13 @@
         <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8095,7 +8099,7 @@
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>21</v>
@@ -8137,7 +8141,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>92</v>
@@ -8169,10 +8173,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8195,13 +8199,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8232,7 +8236,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -8250,7 +8254,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8282,13 +8286,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>21</v>
@@ -8399,10 +8403,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8514,10 +8518,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8631,10 +8635,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8660,13 +8664,13 @@
         <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8674,7 +8678,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>21</v>
@@ -8716,7 +8720,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>92</v>
@@ -8748,10 +8752,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8777,10 +8781,10 @@
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8831,7 +8835,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8863,10 +8867,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8892,13 +8896,13 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8906,7 +8910,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>21</v>
@@ -8948,7 +8952,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8980,10 +8984,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9006,13 +9010,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9063,7 +9067,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9095,13 +9099,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>21</v>
@@ -9123,13 +9127,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9192,7 +9196,7 @@
         <v>207</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>21</v>
@@ -9212,10 +9216,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9327,10 +9331,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9444,10 +9448,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9473,13 +9477,13 @@
         <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9487,7 +9491,7 @@
       </c>
       <c r="Q62" s="2"/>
       <c r="R62" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S62" t="s" s="2">
         <v>21</v>
@@ -9529,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>92</v>
@@ -9561,10 +9565,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9590,10 +9594,10 @@
         <v>151</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9620,11 +9624,11 @@
         <v>21</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>21</v>
@@ -9642,7 +9646,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9674,10 +9678,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9789,10 +9793,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9906,10 +9910,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9935,16 +9939,16 @@
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9993,7 +9997,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10011,10 +10015,10 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -10025,10 +10029,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10054,13 +10058,13 @@
         <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10110,7 +10114,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10128,10 +10132,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -10142,10 +10146,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10171,14 +10175,14 @@
         <v>173</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10227,7 +10231,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10245,10 +10249,10 @@
         <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10259,10 +10263,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10288,14 +10292,14 @@
         <v>106</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10344,7 +10348,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10362,10 +10366,10 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10376,10 +10380,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10402,19 +10406,19 @@
         <v>93</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10463,7 +10467,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10481,10 +10485,10 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
@@ -10495,13 +10499,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>21</v>
@@ -10523,13 +10527,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>206</v>
@@ -10614,13 +10618,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>21</v>
@@ -10642,13 +10646,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>206</v>
@@ -10733,13 +10737,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>21</v>
@@ -10761,13 +10765,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>206</v>
@@ -10852,13 +10856,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D74" t="s" s="2">
         <v>21</v>
@@ -10880,13 +10884,13 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10969,19 +10973,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>81</v>
@@ -10999,13 +11003,13 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="M75" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11088,19 +11092,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>81</v>
@@ -11118,13 +11122,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L76" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="M76" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11207,19 +11211,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>197</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>81</v>
@@ -11237,13 +11241,13 @@
         <v>21</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L77" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="M77" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11326,10 +11330,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11355,16 +11359,16 @@
         <v>113</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>116</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
@@ -11413,7 +11417,7 @@
         <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11445,10 +11449,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11471,17 +11475,17 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>21</v>
@@ -11530,7 +11534,7 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11545,27 +11549,27 @@
         <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11677,10 +11681,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11794,10 +11798,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11823,16 +11827,16 @@
         <v>173</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>21</v>
@@ -11857,13 +11861,13 @@
         <v>21</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -11881,7 +11885,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11902,7 +11906,7 @@
         <v>196</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -11913,10 +11917,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11939,19 +11943,19 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>21</v>
@@ -11979,10 +11983,10 @@
         <v>155</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>21</v>
@@ -12000,7 +12004,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12018,10 +12022,10 @@
         <v>21</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12032,10 +12036,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12061,29 +12065,29 @@
         <v>139</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>21</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>21</v>
@@ -12119,7 +12123,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12137,10 +12141,10 @@
         <v>21</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12151,17 +12155,17 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>92</v>
@@ -12182,13 +12186,13 @@
         <v>106</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12202,7 +12206,7 @@
         <v>21</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>21</v>
@@ -12238,7 +12242,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12256,10 +12260,10 @@
         <v>21</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12270,10 +12274,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12296,13 +12300,13 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12353,7 +12357,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12371,10 +12375,10 @@
         <v>21</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -12385,10 +12389,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12411,16 +12415,16 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12470,7 +12474,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12488,10 +12492,10 @@
         <v>21</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -12502,17 +12506,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>92</v>
@@ -12533,10 +12537,10 @@
         <v>106</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12587,7 +12591,7 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12602,7 +12606,7 @@
         <v>104</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>21</v>
@@ -12611,7 +12615,7 @@
         <v>21</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>21</v>
@@ -12619,10 +12623,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12645,13 +12649,13 @@
         <v>93</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12702,7 +12706,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12717,16 +12721,16 @@
         <v>104</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>21</v>
@@ -12734,14 +12738,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12760,17 +12764,17 @@
         <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -12819,7 +12823,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12834,13 +12838,13 @@
         <v>104</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
@@ -12851,17 +12855,17 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>92</v>
@@ -12882,10 +12886,10 @@
         <v>173</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12912,13 +12916,13 @@
         <v>21</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>21</v>
@@ -12936,7 +12940,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>92</v>
@@ -12951,27 +12955,27 @@
         <v>104</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12994,13 +12998,13 @@
         <v>93</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13030,10 +13034,10 @@
         <v>155</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -13051,7 +13055,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13066,7 +13070,7 @@
         <v>104</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>21</v>
@@ -13083,10 +13087,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13109,13 +13113,13 @@
         <v>93</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13145,10 +13149,10 @@
         <v>163</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13166,7 +13170,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13181,7 +13185,7 @@
         <v>104</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>21</v>
@@ -13190,7 +13194,7 @@
         <v>21</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>21</v>
@@ -13198,10 +13202,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13224,13 +13228,13 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13260,7 +13264,7 @@
         <v>163</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Z94" t="s" s="2">
         <v>21</v>
@@ -13281,7 +13285,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13296,7 +13300,7 @@
         <v>104</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>21</v>
@@ -13305,7 +13309,7 @@
         <v>21</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>21</v>
@@ -13313,10 +13317,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13339,13 +13343,13 @@
         <v>93</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13375,7 +13379,7 @@
         <v>163</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z95" t="s" s="2">
         <v>21</v>
@@ -13396,7 +13400,7 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13411,7 +13415,7 @@
         <v>104</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>21</v>
@@ -13420,18 +13424,18 @@
         <v>21</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13454,13 +13458,13 @@
         <v>93</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13490,10 +13494,10 @@
         <v>163</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -13511,7 +13515,7 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13526,7 +13530,7 @@
         <v>104</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>21</v>
@@ -13535,18 +13539,18 @@
         <v>21</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13569,13 +13573,13 @@
         <v>93</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13626,7 +13630,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13641,7 +13645,7 @@
         <v>104</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>21</v>
@@ -13650,7 +13654,7 @@
         <v>21</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>21</v>
@@ -13658,10 +13662,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13684,13 +13688,13 @@
         <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13741,7 +13745,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13756,7 +13760,7 @@
         <v>104</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>21</v>
@@ -13765,7 +13769,7 @@
         <v>21</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>21</v>
@@ -13773,10 +13777,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13799,13 +13803,13 @@
         <v>93</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13835,7 +13839,7 @@
         <v>163</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z99" t="s" s="2">
         <v>21</v>
@@ -13856,7 +13860,7 @@
         <v>21</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -13871,7 +13875,7 @@
         <v>104</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>21</v>
@@ -13880,7 +13884,7 @@
         <v>21</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>21</v>
@@ -13888,10 +13892,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13914,13 +13918,13 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13950,10 +13954,10 @@
         <v>155</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -13971,7 +13975,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -13986,7 +13990,7 @@
         <v>104</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>21</v>
@@ -14003,17 +14007,17 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>92</v>
@@ -14031,13 +14035,13 @@
         <v>21</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14088,7 +14092,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14103,7 +14107,7 @@
         <v>104</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>21</v>
@@ -14112,7 +14116,7 @@
         <v>21</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>21</v>
@@ -14120,14 +14124,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14146,16 +14150,16 @@
         <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14205,7 +14209,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14220,31 +14224,31 @@
         <v>104</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14263,13 +14267,13 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14320,7 +14324,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14335,27 +14339,27 @@
         <v>104</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14378,13 +14382,13 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14435,7 +14439,7 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14450,27 +14454,27 @@
         <v>104</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14493,13 +14497,13 @@
         <v>93</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14550,7 +14554,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14565,7 +14569,7 @@
         <v>104</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>21</v>
@@ -14574,18 +14578,18 @@
         <v>21</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14608,13 +14612,13 @@
         <v>93</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14665,7 +14669,7 @@
         <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14680,7 +14684,7 @@
         <v>104</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL106" t="s" s="2">
         <v>21</v>
@@ -14689,18 +14693,18 @@
         <v>21</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14723,13 +14727,13 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14759,10 +14763,10 @@
         <v>163</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -14780,7 +14784,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -14795,7 +14799,7 @@
         <v>104</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>21</v>
@@ -14804,18 +14808,18 @@
         <v>21</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14838,13 +14842,13 @@
         <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14895,7 +14899,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -14910,13 +14914,13 @@
         <v>104</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
@@ -14927,10 +14931,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14953,13 +14957,13 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15010,7 +15014,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15025,7 +15029,7 @@
         <v>104</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>21</v>
@@ -15034,7 +15038,7 @@
         <v>21</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>21</v>
@@ -15042,10 +15046,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15157,10 +15161,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15274,14 +15278,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15303,16 +15307,16 @@
         <v>113</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>116</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>21</v>
@@ -15361,7 +15365,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15393,10 +15397,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15422,10 +15426,10 @@
         <v>106</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15476,7 +15480,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>92</v>
@@ -15491,7 +15495,7 @@
         <v>104</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AL113" t="s" s="2">
         <v>21</v>
@@ -15500,7 +15504,7 @@
         <v>21</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>21</v>
@@ -15508,10 +15512,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15534,13 +15538,13 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15591,7 +15595,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15606,7 +15610,7 @@
         <v>104</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>21</v>
@@ -15615,7 +15619,7 @@
         <v>21</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>21</v>
@@ -15623,10 +15627,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15652,10 +15656,10 @@
         <v>106</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15706,7 +15710,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -15721,7 +15725,7 @@
         <v>104</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>21</v>
@@ -15730,7 +15734,7 @@
         <v>21</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>21</v>
@@ -15738,10 +15742,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15764,13 +15768,13 @@
         <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15821,7 +15825,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -15836,7 +15840,7 @@
         <v>104</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>21</v>
@@ -15853,10 +15857,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15968,10 +15972,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16085,14 +16089,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16114,16 +16118,16 @@
         <v>113</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>116</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16172,7 +16176,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -16204,10 +16208,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16233,10 +16237,10 @@
         <v>106</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16287,7 +16291,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16302,7 +16306,7 @@
         <v>104</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>21</v>
@@ -16319,10 +16323,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16345,13 +16349,13 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16381,10 +16385,10 @@
         <v>177</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>21</v>
@@ -16402,7 +16406,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -16417,7 +16421,7 @@
         <v>104</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>21</v>
